--- a/folder_template/Template0_AI Usage Report.xlsx
+++ b/folder_template/Template0_AI Usage Report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="149">
   <si>
     <t xml:space="preserve">SWP391- Project AI Usage Report </t>
   </si>
@@ -101,13 +101,16 @@
     <t>Võ Thành Đạt (Leader)</t>
   </si>
   <si>
-    <t>Chat GPT, Antigravity, Gemini , Claude</t>
+    <t>Antigravity, Gemini</t>
   </si>
   <si>
     <t>SE193987</t>
   </si>
   <si>
     <t>Cao Nhật Lâm</t>
+  </si>
+  <si>
+    <t>Chat GPT, Antigravity, Gemini , Claude</t>
   </si>
   <si>
     <t>SE193985</t>
@@ -1498,9 +1501,9 @@
   <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="21.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="32.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="32.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="30.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="32.552380952381" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:5">
@@ -1589,7 +1592,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
     </row>
-    <row r="9" ht="13.2" spans="1:5">
+    <row r="9" ht="12.75" spans="1:5">
       <c r="B9" s="22"/>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5">
@@ -1618,7 +1621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="13.2" spans="1:5">
+    <row r="12" spans="1:5">
       <c r="A12" s="23">
         <v>1</v>
       </c>
@@ -1635,7 +1638,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="13.2" spans="1:5">
+    <row r="13" ht="12.75" spans="1:5">
       <c r="A13" s="23">
         <v>2</v>
       </c>
@@ -1649,58 +1652,58 @@
         <v>12</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="14" ht="13.2" spans="1:5">
+    <row r="14" ht="12.75" spans="1:5">
       <c r="A14" s="23">
         <v>3</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="15" ht="13.2" spans="1:5">
+    <row r="15" ht="12.75" spans="1:5">
       <c r="A15" s="23">
         <v>4</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="16" ht="13.2" spans="1:5">
+    <row r="16" ht="12.75" spans="1:5">
       <c r="A16" s="23">
         <v>5</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1719,49 +1722,49 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
-    <col min="2" max="2" width="18.8888888888889" customWidth="1"/>
-    <col min="3" max="3" width="18.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="9.21904761904762" customWidth="1"/>
+    <col min="2" max="2" width="18.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="18.552380952381" customWidth="1"/>
     <col min="5" max="5" width="20.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="23.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="23.2190476190476" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="13.4444444444444" customWidth="1"/>
-    <col min="10" max="10" width="25.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="15.8857142857143" customWidth="1"/>
+    <col min="9" max="9" width="13.447619047619" customWidth="1"/>
+    <col min="10" max="10" width="25.552380952381" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" s="14"/>
       <c r="L1" s="14"/>
@@ -1784,31 +1787,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I2" s="11">
         <v>5</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
@@ -1831,31 +1834,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I3" s="11">
         <v>5</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
@@ -1878,31 +1881,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I4" s="11">
         <v>4</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" ht="62.5" customHeight="1" spans="1:25">
@@ -1910,95 +1913,95 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I5" s="11">
         <v>4</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" ht="92.4" spans="1:25">
-      <c r="A6" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="11" t="s">
+    </row>
+    <row r="6" ht="89.25" spans="1:25">
+      <c r="A6" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="11" t="s">
         <v>72</v>
       </c>
+      <c r="C6" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="D6" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" ht="92.4" spans="1:25">
-      <c r="A7" s="11" t="s">
         <v>78</v>
       </c>
+    </row>
+    <row r="7" ht="89.25" spans="1:25">
+      <c r="A7" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="B7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="J7" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2013,51 +2016,51 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="10.1111111111111" style="9" customWidth="1"/>
-    <col min="2" max="2" width="22.8888888888889" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.1142857142857" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.8857142857143" style="9" customWidth="1"/>
     <col min="3" max="3" width="19" style="9" customWidth="1"/>
     <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
     <col min="5" max="5" width="20.6666666666667" style="9" customWidth="1"/>
     <col min="6" max="6" width="25.3333333333333" style="9" customWidth="1"/>
-    <col min="7" max="7" width="16.5555555555556" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.552380952381" style="9" customWidth="1"/>
     <col min="8" max="8" width="24.3333333333333" style="9" customWidth="1"/>
-    <col min="9" max="9" width="13.2222222222222" style="9" customWidth="1"/>
-    <col min="10" max="10" width="29.4444444444444" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.2190476190476" style="9" customWidth="1"/>
+    <col min="10" max="10" width="29.447619047619" style="9" customWidth="1"/>
     <col min="11" max="16384" width="12.6666666666667" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
@@ -2077,34 +2080,34 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:25">
       <c r="A2" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -2115,34 +2118,34 @@
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:25">
       <c r="A3" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
@@ -2151,196 +2154,196 @@
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" ht="118.8" spans="1:25">
+    <row r="4" ht="114.75" spans="1:25">
       <c r="A4" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" ht="63.75" spans="1:25">
+      <c r="A5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" ht="89.25" spans="1:25">
+      <c r="A6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" ht="66" spans="1:25">
-      <c r="A5" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" ht="79.2" spans="1:25">
-      <c r="A6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" ht="92.4" spans="1:25">
+    </row>
+    <row r="7" ht="102" spans="1:25">
       <c r="A7" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="8" ht="105.6" spans="1:25">
+    <row r="8" ht="114.75" spans="1:25">
       <c r="A8" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="9" ht="92.4" spans="1:25">
+    <row r="9" ht="89.25" spans="1:25">
       <c r="A9" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2355,18 +2358,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="27.1111111111111" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1142857142857" style="1" customWidth="1"/>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:26">
       <c r="A1" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2395,10 +2398,10 @@
     </row>
     <row r="2" ht="19.8" customHeight="1" spans="1:26">
       <c r="A2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -2427,10 +2430,10 @@
     </row>
     <row r="3" ht="28.8" customHeight="1" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2459,10 +2462,10 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:26">
       <c r="A4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2491,10 +2494,10 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2523,10 +2526,10 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:26">
       <c r="A6" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2555,10 +2558,10 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:26">
       <c r="A7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2587,10 +2590,10 @@
     </row>
     <row r="8" ht="39" customHeight="1" spans="1:26">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2619,10 +2622,10 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:26">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2651,10 +2654,10 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2683,10 +2686,10 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:26">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>

--- a/folder_template/Template0_AI Usage Report.xlsx
+++ b/folder_template/Template0_AI Usage Report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11880"/>
+    <workbookView windowWidth="19200" windowHeight="8000" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -1498,12 +1498,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.8857142857143" customWidth="1"/>
-    <col min="3" max="3" width="30.2190476190476" customWidth="1"/>
-    <col min="5" max="5" width="32.552380952381" customWidth="1"/>
+    <col min="1" max="1" width="21.3363636363636" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.8818181818182" customWidth="1"/>
+    <col min="3" max="3" width="30.2181818181818" customWidth="1"/>
+    <col min="5" max="5" width="32.5545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:5">
@@ -1592,7 +1592,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
     </row>
-    <row r="9" ht="12.75" spans="1:5">
+    <row r="9" ht="12.5" spans="1:5">
       <c r="B9" s="22"/>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5">
@@ -1621,7 +1621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" ht="12.5" spans="1:5">
       <c r="A12" s="23">
         <v>1</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="12.75" spans="1:5">
+    <row r="13" ht="12.5" spans="1:5">
       <c r="A13" s="23">
         <v>2</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="12.75" spans="1:5">
+    <row r="14" ht="12.5" spans="1:5">
       <c r="A14" s="23">
         <v>3</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="12.75" spans="1:5">
+    <row r="15" ht="12.5" spans="1:5">
       <c r="A15" s="23">
         <v>4</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" ht="12.75" spans="1:5">
+    <row r="16" ht="12.5" spans="1:5">
       <c r="A16" s="23">
         <v>5</v>
       </c>
@@ -1722,17 +1722,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="12.5" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9.21904761904762" customWidth="1"/>
-    <col min="2" max="2" width="18.8857142857143" customWidth="1"/>
-    <col min="3" max="3" width="18.552380952381" customWidth="1"/>
-    <col min="5" max="5" width="20.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="23.2190476190476" customWidth="1"/>
+    <col min="1" max="1" width="9.21818181818182" customWidth="1"/>
+    <col min="2" max="2" width="18.8818181818182" customWidth="1"/>
+    <col min="3" max="3" width="18.5545454545455" customWidth="1"/>
+    <col min="5" max="5" width="20.6636363636364" customWidth="1"/>
+    <col min="6" max="6" width="23.2181818181818" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15.8857142857143" customWidth="1"/>
-    <col min="9" max="9" width="13.447619047619" customWidth="1"/>
-    <col min="10" max="10" width="25.552380952381" customWidth="1"/>
+    <col min="8" max="8" width="15.8818181818182" customWidth="1"/>
+    <col min="9" max="9" width="13.4454545454545" customWidth="1"/>
+    <col min="10" max="10" width="25.5545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
@@ -1940,7 +1940,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" ht="89.25" spans="1:25">
+    <row r="6" ht="87.5" spans="1:25">
       <c r="A6" s="11" t="s">
         <v>71</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" ht="89.25" spans="1:25">
+    <row r="7" ht="87.5" spans="1:25">
       <c r="A7" s="11" t="s">
         <v>79</v>
       </c>
@@ -2016,19 +2016,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="10.1142857142857" style="9" customWidth="1"/>
-    <col min="2" max="2" width="22.8857142857143" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.1181818181818" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.8818181818182" style="9" customWidth="1"/>
     <col min="3" max="3" width="19" style="9" customWidth="1"/>
-    <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.6666666666667" style="9" customWidth="1"/>
-    <col min="6" max="6" width="25.3333333333333" style="9" customWidth="1"/>
-    <col min="7" max="7" width="16.552380952381" style="9" customWidth="1"/>
-    <col min="8" max="8" width="24.3333333333333" style="9" customWidth="1"/>
-    <col min="9" max="9" width="13.2190476190476" style="9" customWidth="1"/>
-    <col min="10" max="10" width="29.447619047619" style="9" customWidth="1"/>
-    <col min="11" max="16384" width="12.6666666666667" style="9" customWidth="1"/>
+    <col min="4" max="4" width="12.6636363636364" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.6636363636364" style="9" customWidth="1"/>
+    <col min="6" max="6" width="25.3363636363636" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.5545454545455" style="9" customWidth="1"/>
+    <col min="8" max="8" width="24.3363636363636" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.2181818181818" style="9" customWidth="1"/>
+    <col min="10" max="10" width="29.4454545454545" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="12.6636363636364" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
@@ -2154,7 +2154,7 @@
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" ht="114.75" spans="1:25">
+    <row r="4" ht="112.5" spans="1:25">
       <c r="A4" s="11" t="s">
         <v>102</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" ht="63.75" spans="1:25">
+    <row r="5" ht="50" spans="1:25">
       <c r="A5" s="11" t="s">
         <v>93</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" ht="89.25" spans="1:25">
+    <row r="6" ht="75" spans="1:25">
       <c r="A6" s="13" t="s">
         <v>71</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" ht="102" spans="1:25">
+    <row r="7" ht="87.5" spans="1:25">
       <c r="A7" s="13" t="s">
         <v>79</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" ht="114.75" spans="1:25">
+    <row r="8" ht="87.5" spans="1:25">
       <c r="A8" s="13" t="s">
         <v>125</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" ht="89.25" spans="1:25">
+    <row r="9" ht="87.5" spans="1:25">
       <c r="A9" s="13" t="s">
         <v>131</v>
       </c>
@@ -2358,9 +2358,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="27.1142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1181818181818" style="1" customWidth="1"/>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>

--- a/folder_template/Template0_AI Usage Report.xlsx
+++ b/folder_template/Template0_AI Usage Report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -1498,12 +1498,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.3363636363636" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.8818181818182" customWidth="1"/>
-    <col min="3" max="3" width="30.2181818181818" customWidth="1"/>
-    <col min="5" max="5" width="32.5545454545455" customWidth="1"/>
+    <col min="1" max="1" width="21.3333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.8796296296296" customWidth="1"/>
+    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="32.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:5">
@@ -1592,7 +1592,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
     </row>
-    <row r="9" ht="12.5" spans="1:5">
+    <row r="9" ht="13.2" spans="1:5">
       <c r="B9" s="22"/>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5">
@@ -1621,7 +1621,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="12.5" spans="1:5">
+    <row r="12" ht="13.2" spans="1:5">
       <c r="A12" s="23">
         <v>1</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="12.5" spans="1:5">
+    <row r="13" ht="13.2" spans="1:5">
       <c r="A13" s="23">
         <v>2</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="12.5" spans="1:5">
+    <row r="14" ht="13.2" spans="1:5">
       <c r="A14" s="23">
         <v>3</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="12.5" spans="1:5">
+    <row r="15" ht="13.2" spans="1:5">
       <c r="A15" s="23">
         <v>4</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" ht="12.5" spans="1:5">
+    <row r="16" ht="13.2" spans="1:5">
       <c r="A16" s="23">
         <v>5</v>
       </c>
@@ -1722,17 +1722,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="12.5" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9.21818181818182" customWidth="1"/>
-    <col min="2" max="2" width="18.8818181818182" customWidth="1"/>
-    <col min="3" max="3" width="18.5545454545455" customWidth="1"/>
-    <col min="5" max="5" width="20.6636363636364" customWidth="1"/>
-    <col min="6" max="6" width="23.2181818181818" customWidth="1"/>
+    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
+    <col min="2" max="2" width="18.8796296296296" customWidth="1"/>
+    <col min="3" max="3" width="18.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="20.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="23.2222222222222" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15.8818181818182" customWidth="1"/>
-    <col min="9" max="9" width="13.4454545454545" customWidth="1"/>
-    <col min="10" max="10" width="25.5545454545455" customWidth="1"/>
+    <col min="8" max="8" width="15.8796296296296" customWidth="1"/>
+    <col min="9" max="9" width="13.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="25.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
@@ -1940,7 +1940,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" ht="87.5" spans="1:25">
+    <row r="6" ht="92.4" spans="1:25">
       <c r="A6" s="11" t="s">
         <v>71</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" ht="87.5" spans="1:25">
+    <row r="7" ht="92.4" spans="1:25">
       <c r="A7" s="11" t="s">
         <v>79</v>
       </c>
@@ -2016,19 +2016,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="10.1181818181818" style="9" customWidth="1"/>
-    <col min="2" max="2" width="22.8818181818182" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.1203703703704" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.8796296296296" style="9" customWidth="1"/>
     <col min="3" max="3" width="19" style="9" customWidth="1"/>
-    <col min="4" max="4" width="12.6636363636364" style="9" customWidth="1"/>
-    <col min="5" max="5" width="20.6636363636364" style="9" customWidth="1"/>
-    <col min="6" max="6" width="25.3363636363636" style="9" customWidth="1"/>
-    <col min="7" max="7" width="16.5545454545455" style="9" customWidth="1"/>
-    <col min="8" max="8" width="24.3363636363636" style="9" customWidth="1"/>
-    <col min="9" max="9" width="13.2181818181818" style="9" customWidth="1"/>
-    <col min="10" max="10" width="29.4454545454545" style="9" customWidth="1"/>
-    <col min="11" max="16384" width="12.6636363636364" style="9" customWidth="1"/>
+    <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
+    <col min="5" max="5" width="20.6666666666667" style="9" customWidth="1"/>
+    <col min="6" max="6" width="25.3333333333333" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.5555555555556" style="9" customWidth="1"/>
+    <col min="8" max="8" width="24.3333333333333" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.2222222222222" style="9" customWidth="1"/>
+    <col min="10" max="10" width="29.4444444444444" style="9" customWidth="1"/>
+    <col min="11" max="16384" width="12.6666666666667" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
@@ -2154,7 +2154,7 @@
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" ht="112.5" spans="1:25">
+    <row r="4" ht="118.8" spans="1:25">
       <c r="A4" s="11" t="s">
         <v>102</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" ht="50" spans="1:25">
+    <row r="5" ht="66" spans="1:25">
       <c r="A5" s="11" t="s">
         <v>93</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" ht="75" spans="1:25">
+    <row r="6" ht="79.2" spans="1:25">
       <c r="A6" s="13" t="s">
         <v>71</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" ht="87.5" spans="1:25">
+    <row r="7" ht="92.4" spans="1:25">
       <c r="A7" s="13" t="s">
         <v>79</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" ht="87.5" spans="1:25">
+    <row r="8" ht="105.6" spans="1:25">
       <c r="A8" s="13" t="s">
         <v>125</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" ht="87.5" spans="1:25">
+    <row r="9" ht="92.4" spans="1:25">
       <c r="A9" s="13" t="s">
         <v>131</v>
       </c>
@@ -2358,9 +2358,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6636363636364" defaultRowHeight="12.5"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="27.1181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1203703703704" style="1" customWidth="1"/>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>

--- a/folder_template/Template0_AI Usage Report.xlsx
+++ b/folder_template/Template0_AI Usage Report.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="28800" windowHeight="11880"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="151">
   <si>
     <t xml:space="preserve">SWP391- Project AI Usage Report </t>
   </si>
@@ -125,10 +125,16 @@
     <t>Đỗ Quốc Huy</t>
   </si>
   <si>
+    <t>Chat GPT, Antigravity, Gemini</t>
+  </si>
+  <si>
     <t>SE182070</t>
   </si>
   <si>
     <t>Lê Nguyễn Chánh Nghĩa</t>
+  </si>
+  <si>
+    <t>Antigravity, Gemini, Figma</t>
   </si>
   <si>
     <t>No.</t>
@@ -1501,9 +1507,9 @@
   <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="21.3333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.8796296296296" customWidth="1"/>
-    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
-    <col min="5" max="5" width="32.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="32.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="30.2190476190476" customWidth="1"/>
+    <col min="5" max="5" width="32.552380952381" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:5">
@@ -1592,7 +1598,7 @@
       <c r="D8" s="21"/>
       <c r="E8" s="21"/>
     </row>
-    <row r="9" ht="13.2" spans="1:5">
+    <row r="9" ht="12.75" spans="1:5">
       <c r="B9" s="22"/>
     </row>
     <row r="10" ht="13" customHeight="1" spans="1:5">
@@ -1621,7 +1627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="13.2" spans="1:5">
+    <row r="12" ht="12.75" spans="1:5">
       <c r="A12" s="23">
         <v>1</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="13.2" spans="1:5">
+    <row r="13" ht="12.75" spans="1:5">
       <c r="A13" s="23">
         <v>2</v>
       </c>
@@ -1655,7 +1661,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="13.2" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14" s="23">
         <v>3</v>
       </c>
@@ -1672,7 +1678,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="13.2" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15" s="23">
         <v>4</v>
       </c>
@@ -1686,24 +1692,24 @@
         <v>12</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="16" ht="13.2" spans="1:5">
+    <row r="16" spans="1:5">
       <c r="A16" s="23">
         <v>5</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1722,49 +1728,49 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2" outlineLevelRow="6"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
-    <col min="2" max="2" width="18.8796296296296" customWidth="1"/>
-    <col min="3" max="3" width="18.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="9.21904761904762" customWidth="1"/>
+    <col min="2" max="2" width="18.8857142857143" customWidth="1"/>
+    <col min="3" max="3" width="18.552380952381" customWidth="1"/>
     <col min="5" max="5" width="20.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="23.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="23.2190476190476" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="15.8796296296296" customWidth="1"/>
-    <col min="9" max="9" width="13.4444444444444" customWidth="1"/>
-    <col min="10" max="10" width="25.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="15.8857142857143" customWidth="1"/>
+    <col min="9" max="9" width="13.447619047619" customWidth="1"/>
+    <col min="10" max="10" width="25.552380952381" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" s="14"/>
       <c r="L1" s="14"/>
@@ -1787,31 +1793,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I2" s="11">
         <v>5</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
@@ -1834,31 +1840,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I3" s="11">
         <v>5</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
@@ -1881,31 +1887,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I4" s="11">
         <v>4</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" ht="62.5" customHeight="1" spans="1:25">
@@ -1913,95 +1919,95 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I5" s="11">
         <v>4</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="6" ht="92.4" spans="1:25">
+    <row r="6" ht="89.25" spans="1:25">
       <c r="A6" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>45</v>
+      <c r="J6" s="11" t="s">
+        <v>80</v>
       </c>
-      <c r="E6" s="11" t="s">
+    </row>
+    <row r="7" ht="89.25" spans="1:25">
+      <c r="A7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" ht="92.4" spans="1:25">
-      <c r="A7" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>72</v>
-      </c>
       <c r="C7" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2016,51 +2022,51 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="10.1203703703704" style="9" customWidth="1"/>
-    <col min="2" max="2" width="22.8796296296296" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.1142857142857" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.8857142857143" style="9" customWidth="1"/>
     <col min="3" max="3" width="19" style="9" customWidth="1"/>
     <col min="4" max="4" width="12.6666666666667" style="9" customWidth="1"/>
     <col min="5" max="5" width="20.6666666666667" style="9" customWidth="1"/>
     <col min="6" max="6" width="25.3333333333333" style="9" customWidth="1"/>
-    <col min="7" max="7" width="16.5555555555556" style="9" customWidth="1"/>
+    <col min="7" max="7" width="16.552380952381" style="9" customWidth="1"/>
     <col min="8" max="8" width="24.3333333333333" style="9" customWidth="1"/>
-    <col min="9" max="9" width="13.2222222222222" style="9" customWidth="1"/>
-    <col min="10" max="10" width="29.4444444444444" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.2190476190476" style="9" customWidth="1"/>
+    <col min="10" max="10" width="29.447619047619" style="9" customWidth="1"/>
     <col min="11" max="16384" width="12.6666666666667" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:25">
       <c r="A1" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
@@ -2080,34 +2086,34 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:25">
       <c r="A2" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
@@ -2118,34 +2124,34 @@
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:25">
       <c r="A3" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="J3" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
@@ -2154,196 +2160,196 @@
       <c r="O3" s="12"/>
       <c r="P3" s="12"/>
     </row>
-    <row r="4" ht="118.8" spans="1:25">
+    <row r="4" ht="114.75" spans="1:25">
       <c r="A4" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" ht="63.75" spans="1:25">
+      <c r="A5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" ht="89.25" spans="1:25">
+      <c r="A6" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" ht="66" spans="1:25">
-      <c r="A5" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" ht="79.2" spans="1:25">
-      <c r="A6" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" ht="92.4" spans="1:25">
+    </row>
+    <row r="7" ht="102" spans="1:25">
       <c r="A7" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="8" ht="105.6" spans="1:25">
+    <row r="8" ht="114.75" spans="1:25">
       <c r="A8" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
-    <row r="9" ht="92.4" spans="1:25">
+    <row r="9" ht="89.25" spans="1:25">
       <c r="A9" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -2358,18 +2364,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="27.1203703703704" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.1142857142857" style="1" customWidth="1"/>
     <col min="2" max="2" width="93" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="1:26">
       <c r="A1" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2398,10 +2404,10 @@
     </row>
     <row r="2" ht="19.8" customHeight="1" spans="1:26">
       <c r="A2" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -2430,10 +2436,10 @@
     </row>
     <row r="3" ht="28.8" customHeight="1" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2462,10 +2468,10 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:26">
       <c r="A4" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -2494,10 +2500,10 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2526,10 +2532,10 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:26">
       <c r="A6" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2558,10 +2564,10 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:26">
       <c r="A7" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -2590,10 +2596,10 @@
     </row>
     <row r="8" ht="39" customHeight="1" spans="1:26">
       <c r="A8" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -2622,10 +2628,10 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:26">
       <c r="A9" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -2654,10 +2660,10 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -2686,10 +2692,10 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:26">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
